--- a/astro-site/public/dl/guia-restaurante-nikkei/calculadora-capex.xlsx
+++ b/astro-site/public/dl/guia-restaurante-nikkei/calculadora-capex.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAPEX Desglosado" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'CAPEX Desglosado'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -521,9 +523,9 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -543,6 +545,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -571,10 +574,19 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Celdas verdes = campos editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/guia-restaurante-nikkei · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -583,7 +595,16 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -592,7 +613,7 @@
   <sheetPr>
     <tabColor rgb="00FF9800"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -621,6 +642,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -683,7 +705,7 @@
       <c r="E5" s="10" t="n"/>
       <c r="F5" s="11">
         <f>E5-D5</f>
-        <v/>
+        <v>-110000.0</v>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
@@ -712,7 +734,7 @@
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="11">
         <f>E6-D6</f>
-        <v/>
+        <v>-14000.0</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
@@ -741,7 +763,7 @@
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="11">
         <f>E7-D7</f>
-        <v/>
+        <v>-9000.0</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
@@ -770,7 +792,7 @@
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="11">
         <f>E8-D8</f>
-        <v/>
+        <v>-10000.0</v>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
@@ -799,7 +821,7 @@
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="11">
         <f>E9-D9</f>
-        <v/>
+        <v>-12000.0</v>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
@@ -828,7 +850,7 @@
       <c r="E10" s="10" t="n"/>
       <c r="F10" s="11">
         <f>E10-D10</f>
-        <v/>
+        <v>-3200.0</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -857,7 +879,7 @@
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="11">
         <f>E11-D11</f>
-        <v/>
+        <v>-6500.0</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -886,7 +908,7 @@
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="11">
         <f>E12-D12</f>
-        <v/>
+        <v>-2800.0</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -915,7 +937,7 @@
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="11">
         <f>E13-D13</f>
-        <v/>
+        <v>-5500.0</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -944,7 +966,7 @@
       <c r="E14" s="10" t="n"/>
       <c r="F14" s="11">
         <f>E14-D14</f>
-        <v/>
+        <v>-8500.0</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -973,7 +995,7 @@
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="11">
         <f>E15-D15</f>
-        <v/>
+        <v>-4500.0</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -1002,7 +1024,7 @@
       <c r="E16" s="10" t="n"/>
       <c r="F16" s="11">
         <f>E16-D16</f>
-        <v/>
+        <v>-2800.0</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -1031,7 +1053,7 @@
       <c r="E17" s="10" t="n"/>
       <c r="F17" s="11">
         <f>E17-D17</f>
-        <v/>
+        <v>-1200.0</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1060,7 +1082,7 @@
       <c r="E18" s="10" t="n"/>
       <c r="F18" s="11">
         <f>E18-D18</f>
-        <v/>
+        <v>-12000.0</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1089,7 +1111,7 @@
       <c r="E19" s="10" t="n"/>
       <c r="F19" s="11">
         <f>E19-D19</f>
-        <v/>
+        <v>-5000.0</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1118,7 +1140,7 @@
       <c r="E20" s="10" t="n"/>
       <c r="F20" s="11">
         <f>E20-D20</f>
-        <v/>
+        <v>-2500.0</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1147,7 +1169,7 @@
       <c r="E21" s="10" t="n"/>
       <c r="F21" s="11">
         <f>E21-D21</f>
-        <v/>
+        <v>-2500.0</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1176,7 +1198,7 @@
       <c r="E22" s="10" t="n"/>
       <c r="F22" s="11">
         <f>E22-D22</f>
-        <v/>
+        <v>-6000.0</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1205,7 +1227,7 @@
       <c r="E23" s="10" t="n"/>
       <c r="F23" s="11">
         <f>E23-D23</f>
-        <v/>
+        <v>-4500.0</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1234,7 +1256,7 @@
       <c r="E24" s="10" t="n"/>
       <c r="F24" s="11">
         <f>E24-D24</f>
-        <v/>
+        <v>-5500.0</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1263,7 +1285,7 @@
       <c r="E25" s="10" t="n"/>
       <c r="F25" s="11">
         <f>E25-D25</f>
-        <v/>
+        <v>-10000.0</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1292,7 +1314,7 @@
       <c r="E26" s="10" t="n"/>
       <c r="F26" s="11">
         <f>E26-D26</f>
-        <v/>
+        <v>-3500.0</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1321,7 +1343,7 @@
       <c r="E27" s="10" t="n"/>
       <c r="F27" s="11">
         <f>E27-D27</f>
-        <v/>
+        <v>-9000.0</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1350,7 +1372,7 @@
       <c r="E28" s="10" t="n"/>
       <c r="F28" s="11">
         <f>E28-D28</f>
-        <v/>
+        <v>-4500.0</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1379,7 +1401,7 @@
       <c r="E29" s="10" t="n"/>
       <c r="F29" s="11">
         <f>E29-D29</f>
-        <v/>
+        <v>-2500.0</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -1408,7 +1430,7 @@
       <c r="E30" s="10" t="n"/>
       <c r="F30" s="11">
         <f>E30-D30</f>
-        <v/>
+        <v>-12000.0</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -1437,7 +1459,7 @@
       <c r="E31" s="10" t="n"/>
       <c r="F31" s="11">
         <f>E31-D31</f>
-        <v/>
+        <v>-26000.0</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -1466,7 +1488,7 @@
       <c r="E32" s="10" t="n"/>
       <c r="F32" s="11">
         <f>E32-D32</f>
-        <v/>
+        <v>-20000.0</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -1495,7 +1517,7 @@
       <c r="E33" s="10" t="n"/>
       <c r="F33" s="11">
         <f>E33-D33</f>
-        <v/>
+        <v>-5000.0</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -1524,7 +1546,7 @@
       <c r="E34" s="10" t="n"/>
       <c r="F34" s="11">
         <f>E34-D34</f>
-        <v/>
+        <v>-7000.0</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -1553,7 +1575,7 @@
       <c r="E35" s="10" t="n"/>
       <c r="F35" s="11">
         <f>E35-D35</f>
-        <v/>
+        <v>-12500.0</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -1582,7 +1604,7 @@
       <c r="E36" s="10" t="n"/>
       <c r="F36" s="11">
         <f>E36-D36</f>
-        <v/>
+        <v>-10000.0</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -1611,7 +1633,7 @@
       <c r="E37" s="10" t="n"/>
       <c r="F37" s="11">
         <f>E37-D37</f>
-        <v/>
+        <v>-15000.0</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -1640,7 +1662,7 @@
       <c r="E38" s="10" t="n"/>
       <c r="F38" s="11">
         <f>E38-D38</f>
-        <v/>
+        <v>-5000.0</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -1669,7 +1691,7 @@
       <c r="E39" s="10" t="n"/>
       <c r="F39" s="11">
         <f>E39-D39</f>
-        <v/>
+        <v>-70000.0</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -1678,6 +1700,7 @@
       </c>
       <c r="H39" s="12" t="n"/>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="C41" s="13" t="inlineStr">
         <is>
@@ -1686,17 +1709,18 @@
       </c>
       <c r="D41" s="14">
         <f>SUM(D5:D39)</f>
-        <v/>
+        <v>440000.0</v>
       </c>
       <c r="E41" s="14">
         <f>SUM(E5:E39)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F41" s="14">
         <f>E41-D41</f>
-        <v/>
-      </c>
-    </row>
+        <v>-440000.0</v>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
@@ -1715,6 +1739,15 @@
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>